--- a/tests/data/riborf/SD3.xlsx
+++ b/tests/data/riborf/SD3.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,512 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" t="n">
+        <v>108112588</v>
+      </c>
+      <c r="C9" t="n">
+        <v>108112594</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ENSMUST00000000001.4:3:-|62|3262:740:746|iORF|ATG</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>108112588</v>
+      </c>
+      <c r="H9" t="n">
+        <v>108112594</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>6,</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" t="n">
+        <v>41543616</v>
+      </c>
+      <c r="C10" t="n">
+        <v>41543631</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ENSMUST00000169595.1:6:+|2|48:20:35|noncoding|TTG</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>41543616</v>
+      </c>
+      <c r="H10" t="n">
+        <v>41543631</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>15,</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>13</v>
+      </c>
+      <c r="B11" t="n">
+        <v>4382678</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4382696</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ENSMUST00000220926.1:13:-|1|166:1:19|noncoding|CTG</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>4382678</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4382696</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>18,</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>18</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57316436</v>
+      </c>
+      <c r="C12" t="n">
+        <v>57316517</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ENSMUST00000235655.1:18:+|5|279:41:122|noncoding|ACG</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>57316436</v>
+      </c>
+      <c r="H12" t="n">
+        <v>57316517</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>81,</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" t="n">
+        <v>11013821</v>
+      </c>
+      <c r="C13" t="n">
+        <v>11013866</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ENSMUST00000192542.1:2:-|4|111:53:98|noncoding|CTG</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>11013821</v>
+      </c>
+      <c r="H13" t="n">
+        <v>11013866</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>45,</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>14</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8214779</v>
+      </c>
+      <c r="C14" t="n">
+        <v>8214902</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ENSMUST00000170111.1:14:+|29|3052:279:402|uORF|ATG</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>8214779</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8214902</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>123,</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8220200</v>
+      </c>
+      <c r="C15" t="n">
+        <v>8222187</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ENSMUST00000170111.1:14:+|160|3052:1658:1679|iORF|ATG</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>8220200</v>
+      </c>
+      <c r="H15" t="n">
+        <v>8222187</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>20,1,</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0,1986,</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" t="n">
+        <v>120447148</v>
+      </c>
+      <c r="C16" t="n">
+        <v>120462104</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ENSMUST00000000087.12:4:+|14|3353:267:459|ouORF|ATG</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>120447148</v>
+      </c>
+      <c r="H16" t="n">
+        <v>120462104</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>13,63,24,92,</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0,6095,6603,14864,</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" t="n">
+        <v>23745051</v>
+      </c>
+      <c r="C17" t="n">
+        <v>23745087</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ENSMUST00000091752.4:13:-|29|630:516:552|odORF|ATG</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>23745051</v>
+      </c>
+      <c r="H17" t="n">
+        <v>23745087</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>36,</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97361217</v>
+      </c>
+      <c r="C18" t="n">
+        <v>97384062</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ENSMUST00000226495.1:15:+|1|441:2:155|uORF|ATG</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>97361217</v>
+      </c>
+      <c r="H18" t="n">
+        <v>97384062</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>118,35,</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0,22810,</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97361217</v>
+      </c>
+      <c r="C19" t="n">
+        <v>97384062</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ENSMUST00000228521.1:15:+|2|1790:17:173|uORF|ATG</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>97361217</v>
+      </c>
+      <c r="H19" t="n">
+        <v>97384062</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>118,38,</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0,22807,</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/data/riborf/SD3.xlsx
+++ b/tests/data/riborf/SD3.xlsx
@@ -8,6 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="mouse" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="zebrafish" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="worm" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="human" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="yeast" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1293,4 +1297,1408 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B1" t="n">
+        <v>2574160</v>
+      </c>
+      <c r="C1" t="n">
+        <v>2574184</v>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ENSDART00000166326:9:+|6|182:40:64|uORF|ATG</t>
+        </is>
+      </c>
+      <c r="E1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G1" t="n">
+        <v>2574160</v>
+      </c>
+      <c r="H1" t="n">
+        <v>2574184</v>
+      </c>
+      <c r="I1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>24,</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B2" t="n">
+        <v>73651774</v>
+      </c>
+      <c r="C2" t="n">
+        <v>73653208</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ENSDART00000185589:7:+|1|177:91:178|truncation|CTG</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>73651774</v>
+      </c>
+      <c r="H2" t="n">
+        <v>73653208</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>74,13,</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0,1421,</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>15694214</v>
+      </c>
+      <c r="C3" t="n">
+        <v>15697261</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ENSDART00000188874:3:-|4|198:40:199|noncoding|ATG</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>15694214</v>
+      </c>
+      <c r="H3" t="n">
+        <v>15697261</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>156,3,</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0,3044,</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B4" t="n">
+        <v>7808930</v>
+      </c>
+      <c r="C4" t="n">
+        <v>7808954</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ENSDART00000157612:23:-|6|330:84:108|iORF|ATG</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>7808930</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7808954</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>24,</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1586108</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1586518</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ENSDART00000160793:22:+|3|184:50:179|truncation|ATG</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1586108</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1586518</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>55,74,</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0,336,</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B6" t="n">
+        <v>26427566</v>
+      </c>
+      <c r="C6" t="n">
+        <v>26427575</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ENSDART00000142246:8:+|3|197:19:28|noncoding|TTG</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>26427566</v>
+      </c>
+      <c r="H6" t="n">
+        <v>26427575</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>9,</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KN150039.1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>78</v>
+      </c>
+      <c r="C7" t="n">
+        <v>763</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ENSDART00000168136:KN150039.1:-|1|165:1:166|canonical|ATG</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>78</v>
+      </c>
+      <c r="H7" t="n">
+        <v>763</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>81,84,</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0,601,</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B8" t="n">
+        <v>54027902</v>
+      </c>
+      <c r="C8" t="n">
+        <v>54034308</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ENSDART00000194892:8:+|18|809:222:603|noncoding|ATG</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>54027902</v>
+      </c>
+      <c r="H8" t="n">
+        <v>54034308</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>34,195,152,</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0,3872,6254,</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B1" t="n">
+        <v>6088011</v>
+      </c>
+      <c r="C1" t="n">
+        <v>6088059</v>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>C45B2.8.1:X:+|4|335:28:76|uORF|ATG</t>
+        </is>
+      </c>
+      <c r="E1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G1" t="n">
+        <v>6088011</v>
+      </c>
+      <c r="H1" t="n">
+        <v>6088059</v>
+      </c>
+      <c r="I1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>48,</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>14477212</v>
+      </c>
+      <c r="C2" t="n">
+        <v>14477266</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>M163.15:X:+|1|72:18:72|noncoding|GTG</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>14477212</v>
+      </c>
+      <c r="H2" t="n">
+        <v>14477266</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>54,</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>13834459</v>
+      </c>
+      <c r="C3" t="n">
+        <v>13834501</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>F08G2.13:II:-|1|75:23:65|noncoding|ATG</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>13834459</v>
+      </c>
+      <c r="H3" t="n">
+        <v>13834501</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>42,</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>10380772</v>
+      </c>
+      <c r="C4" t="n">
+        <v>10380796</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>F45H11.11.1:I:+|2|174:26:50|iORF|CTG</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>10380772</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10380796</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>24,</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>9943426</v>
+      </c>
+      <c r="C5" t="n">
+        <v>9943612</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>T07C12.13.1:V:+|4|225:40:226|truncation|ATG</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>9943426</v>
+      </c>
+      <c r="H5" t="n">
+        <v>9943612</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>186,</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>7200289</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7200295</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>E04F6.16:II:+|2|186:58:64|noncoding|CTG</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>7200289</v>
+      </c>
+      <c r="H6" t="n">
+        <v>7200295</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>6,</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2528649</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2528679</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Y54F10AM.15.1:III:-|1|30:1:31|canonical|ATG</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>2528649</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2528679</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>30,</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>chr12</t>
+        </is>
+      </c>
+      <c r="B1" t="n">
+        <v>106301956</v>
+      </c>
+      <c r="C1" t="n">
+        <v>106301980</v>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ENST00000553143.5:chr12:+|4|153:29:53|uORF|ATG</t>
+        </is>
+      </c>
+      <c r="E1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G1" t="n">
+        <v>106301956</v>
+      </c>
+      <c r="H1" t="n">
+        <v>106301980</v>
+      </c>
+      <c r="I1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>24,</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>chr6</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>31382073</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31382262</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ENST00000425174.1:chr6:-|2|53:27:54|noncoding|GTG</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>31382073</v>
+      </c>
+      <c r="H2" t="n">
+        <v>31382262</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>5,22,</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0,167,</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>chr1</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>242975004</v>
+      </c>
+      <c r="C3" t="n">
+        <v>242975082</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ENST00000438481.1:chr1:+|1|80:1:79|noncoding|ACG</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>242975004</v>
+      </c>
+      <c r="H3" t="n">
+        <v>242975082</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>78,</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>chr7</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>142789016</v>
+      </c>
+      <c r="C4" t="n">
+        <v>142789037</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ENST00000633713.1:chr7:+|2|53:30:51|iORF|ATG</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>142789016</v>
+      </c>
+      <c r="H4" t="n">
+        <v>142789037</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>21,</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>chr7</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>142796372</v>
+      </c>
+      <c r="C5" t="n">
+        <v>142796414</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ENST00000390412.1:chr7:+|1|50:9:51|truncation|ATG</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>142796372</v>
+      </c>
+      <c r="H5" t="n">
+        <v>142796414</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>42,</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>chr8</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>40104186</v>
+      </c>
+      <c r="C6" t="n">
+        <v>40104201</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ENST00000524098.1:chr8:+|1|187:19:34|noncoding|ATG</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>40104186</v>
+      </c>
+      <c r="H6" t="n">
+        <v>40104201</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>15,</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>chr17</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>778789</v>
+      </c>
+      <c r="C7" t="n">
+        <v>782255</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ENST00000625892.1:chr17:-|1|111:1:112|canonical|ATG</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>778789</v>
+      </c>
+      <c r="H7" t="n">
+        <v>782255</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>21,90,</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0,3376,</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>chr14</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>104815596</v>
+      </c>
+      <c r="C8" t="n">
+        <v>104815746</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ENST00000625139.1:chr14:-|1|305:8:158|noncoding|TTG</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>104815596</v>
+      </c>
+      <c r="H8" t="n">
+        <v>104815746</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>150,</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>XIV</t>
+        </is>
+      </c>
+      <c r="B1" t="n">
+        <v>542516</v>
+      </c>
+      <c r="C1" t="n">
+        <v>542822</v>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>YNL046W:XIV:+|18|577:252:558|truncation|ATG</t>
+        </is>
+      </c>
+      <c r="E1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G1" t="n">
+        <v>542516</v>
+      </c>
+      <c r="H1" t="n">
+        <v>542822</v>
+      </c>
+      <c r="I1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>306,</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>XIV</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>635560</v>
+      </c>
+      <c r="C2" t="n">
+        <v>635620</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>YNR004W:XIV:+|7|1320:105:165|uORF|ATG</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>635560</v>
+      </c>
+      <c r="H2" t="n">
+        <v>635620</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>60,</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>XIV</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>359081</v>
+      </c>
+      <c r="C3" t="n">
+        <v>359255</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CUT808:XIV:-|1|352:3:177|noncoding|TTG</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>359081</v>
+      </c>
+      <c r="H3" t="n">
+        <v>359255</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>174,</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>XIV</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>379557</v>
+      </c>
+      <c r="C4" t="n">
+        <v>380873</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>YNL130C:XIV:-|2|1262:19:1243|extension|ATG</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>379557</v>
+      </c>
+      <c r="H4" t="n">
+        <v>380873</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1132,92,</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>XIV</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>538148</v>
+      </c>
+      <c r="C5" t="n">
+        <v>538160</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>YNL048W:XIV:+|4|1816:28:40|uORF|ATG</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>538148</v>
+      </c>
+      <c r="H5" t="n">
+        <v>538160</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>12,</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>XIV</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>627455</v>
+      </c>
+      <c r="C6" t="n">
+        <v>628616</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>YNL001W:XIV:+|5|1312:80:1241|canonical|ATG</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>627455</v>
+      </c>
+      <c r="H6" t="n">
+        <v>628616</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1161,</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/tests/data/riborf/SD3.xlsx
+++ b/tests/data/riborf/SD3.xlsx
@@ -2437,7 +2437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2698,6 +2698,49 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>XIV</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>96963</v>
+      </c>
+      <c r="C7" t="n">
+        <v>101965</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>YNL284C-B:XIV:-|13|5308:288:5289|truncation|ATG</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>96963</v>
+      </c>
+      <c r="H7" t="n">
+        <v>101965</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>3963,1038,</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/data/riborf/SD3.xlsx
+++ b/tests/data/riborf/SD3.xlsx
@@ -8,6 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="mouse" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="zebrafish" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="worm" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="human" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="yeast" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1293,4 +1297,1451 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B1" t="n">
+        <v>2574160</v>
+      </c>
+      <c r="C1" t="n">
+        <v>2574184</v>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ENSDART00000166326:9:+|6|182:40:64|uORF|ATG</t>
+        </is>
+      </c>
+      <c r="E1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G1" t="n">
+        <v>2574160</v>
+      </c>
+      <c r="H1" t="n">
+        <v>2574184</v>
+      </c>
+      <c r="I1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>24,</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B2" t="n">
+        <v>73651774</v>
+      </c>
+      <c r="C2" t="n">
+        <v>73653208</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ENSDART00000185589:7:+|1|177:91:178|truncation|CTG</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>73651774</v>
+      </c>
+      <c r="H2" t="n">
+        <v>73653208</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>74,13,</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0,1421,</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>15694214</v>
+      </c>
+      <c r="C3" t="n">
+        <v>15697261</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ENSDART00000188874:3:-|4|198:40:199|noncoding|ATG</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>15694214</v>
+      </c>
+      <c r="H3" t="n">
+        <v>15697261</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>156,3,</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0,3044,</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B4" t="n">
+        <v>7808930</v>
+      </c>
+      <c r="C4" t="n">
+        <v>7808954</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ENSDART00000157612:23:-|6|330:84:108|iORF|ATG</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>7808930</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7808954</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>24,</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1586108</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1586518</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ENSDART00000160793:22:+|3|184:50:179|truncation|ATG</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1586108</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1586518</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>55,74,</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0,336,</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B6" t="n">
+        <v>26427566</v>
+      </c>
+      <c r="C6" t="n">
+        <v>26427575</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ENSDART00000142246:8:+|3|197:19:28|noncoding|TTG</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>26427566</v>
+      </c>
+      <c r="H6" t="n">
+        <v>26427575</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>9,</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KN150039.1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>78</v>
+      </c>
+      <c r="C7" t="n">
+        <v>763</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ENSDART00000168136:KN150039.1:-|1|165:1:166|canonical|ATG</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>78</v>
+      </c>
+      <c r="H7" t="n">
+        <v>763</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>81,84,</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0,601,</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B8" t="n">
+        <v>54027902</v>
+      </c>
+      <c r="C8" t="n">
+        <v>54034308</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ENSDART00000194892:8:+|18|809:222:603|noncoding|ATG</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>54027902</v>
+      </c>
+      <c r="H8" t="n">
+        <v>54034308</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>34,195,152,</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0,3872,6254,</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B1" t="n">
+        <v>6088011</v>
+      </c>
+      <c r="C1" t="n">
+        <v>6088059</v>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>C45B2.8.1:X:+|4|335:28:76|uORF|ATG</t>
+        </is>
+      </c>
+      <c r="E1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G1" t="n">
+        <v>6088011</v>
+      </c>
+      <c r="H1" t="n">
+        <v>6088059</v>
+      </c>
+      <c r="I1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>48,</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>14477212</v>
+      </c>
+      <c r="C2" t="n">
+        <v>14477266</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>M163.15:X:+|1|72:18:72|noncoding|GTG</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>14477212</v>
+      </c>
+      <c r="H2" t="n">
+        <v>14477266</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>54,</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>13834459</v>
+      </c>
+      <c r="C3" t="n">
+        <v>13834501</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>F08G2.13:II:-|1|75:23:65|noncoding|ATG</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>13834459</v>
+      </c>
+      <c r="H3" t="n">
+        <v>13834501</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>42,</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>10380772</v>
+      </c>
+      <c r="C4" t="n">
+        <v>10380796</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>F45H11.11.1:I:+|2|174:26:50|iORF|CTG</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>10380772</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10380796</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>24,</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>9943426</v>
+      </c>
+      <c r="C5" t="n">
+        <v>9943612</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>T07C12.13.1:V:+|4|225:40:226|truncation|ATG</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>9943426</v>
+      </c>
+      <c r="H5" t="n">
+        <v>9943612</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>186,</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>7200289</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7200295</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>E04F6.16:II:+|2|186:58:64|noncoding|CTG</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>7200289</v>
+      </c>
+      <c r="H6" t="n">
+        <v>7200295</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>6,</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2528649</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2528679</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Y54F10AM.15.1:III:-|1|30:1:31|canonical|ATG</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>2528649</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2528679</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>30,</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>chr12</t>
+        </is>
+      </c>
+      <c r="B1" t="n">
+        <v>106301956</v>
+      </c>
+      <c r="C1" t="n">
+        <v>106301980</v>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ENST00000553143.5:chr12:+|4|153:29:53|uORF|ATG</t>
+        </is>
+      </c>
+      <c r="E1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G1" t="n">
+        <v>106301956</v>
+      </c>
+      <c r="H1" t="n">
+        <v>106301980</v>
+      </c>
+      <c r="I1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>24,</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>chr6</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>31382073</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31382262</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ENST00000425174.1:chr6:-|2|53:27:54|noncoding|GTG</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>31382073</v>
+      </c>
+      <c r="H2" t="n">
+        <v>31382262</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>5,22,</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0,167,</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>chr1</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>242975004</v>
+      </c>
+      <c r="C3" t="n">
+        <v>242975082</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ENST00000438481.1:chr1:+|1|80:1:79|noncoding|ACG</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>242975004</v>
+      </c>
+      <c r="H3" t="n">
+        <v>242975082</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>78,</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>chr7</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>142789016</v>
+      </c>
+      <c r="C4" t="n">
+        <v>142789037</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ENST00000633713.1:chr7:+|2|53:30:51|iORF|ATG</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>142789016</v>
+      </c>
+      <c r="H4" t="n">
+        <v>142789037</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>21,</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>chr7</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>142796372</v>
+      </c>
+      <c r="C5" t="n">
+        <v>142796414</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ENST00000390412.1:chr7:+|1|50:9:51|truncation|ATG</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>142796372</v>
+      </c>
+      <c r="H5" t="n">
+        <v>142796414</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>42,</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>chr8</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>40104186</v>
+      </c>
+      <c r="C6" t="n">
+        <v>40104201</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ENST00000524098.1:chr8:+|1|187:19:34|noncoding|ATG</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>40104186</v>
+      </c>
+      <c r="H6" t="n">
+        <v>40104201</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>15,</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>chr17</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>778789</v>
+      </c>
+      <c r="C7" t="n">
+        <v>782255</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ENST00000625892.1:chr17:-|1|111:1:112|canonical|ATG</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>778789</v>
+      </c>
+      <c r="H7" t="n">
+        <v>782255</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>21,90,</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0,3376,</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>chr14</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>104815596</v>
+      </c>
+      <c r="C8" t="n">
+        <v>104815746</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ENST00000625139.1:chr14:-|1|305:8:158|noncoding|TTG</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>104815596</v>
+      </c>
+      <c r="H8" t="n">
+        <v>104815746</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>150,</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0,</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>XIV</t>
+        </is>
+      </c>
+      <c r="B1" t="n">
+        <v>542516</v>
+      </c>
+      <c r="C1" t="n">
+        <v>542822</v>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>YNL046W:XIV:+|18|577:252:558|truncation|ATG</t>
+        </is>
+      </c>
+      <c r="E1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G1" t="n">
+        <v>542516</v>
+      </c>
+      <c r="H1" t="n">
+        <v>542822</v>
+      </c>
+      <c r="I1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>306,</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>XIV</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>635560</v>
+      </c>
+      <c r="C2" t="n">
+        <v>635620</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>YNR004W:XIV:+|7|1320:105:165|uORF|ATG</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>635560</v>
+      </c>
+      <c r="H2" t="n">
+        <v>635620</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>60,</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>XIV</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>359081</v>
+      </c>
+      <c r="C3" t="n">
+        <v>359255</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CUT808:XIV:-|1|352:3:177|noncoding|TTG</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>359081</v>
+      </c>
+      <c r="H3" t="n">
+        <v>359255</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>174,</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>XIV</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>379557</v>
+      </c>
+      <c r="C4" t="n">
+        <v>380873</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>YNL130C:XIV:-|2|1262:19:1243|extension|ATG</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>379557</v>
+      </c>
+      <c r="H4" t="n">
+        <v>380873</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1132,92,</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>XIV</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>538148</v>
+      </c>
+      <c r="C5" t="n">
+        <v>538160</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>YNL048W:XIV:+|4|1816:28:40|uORF|ATG</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>538148</v>
+      </c>
+      <c r="H5" t="n">
+        <v>538160</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>12,</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>XIV</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>627455</v>
+      </c>
+      <c r="C6" t="n">
+        <v>628616</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>YNL001W:XIV:+|5|1312:80:1241|canonical|ATG</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>627455</v>
+      </c>
+      <c r="H6" t="n">
+        <v>628616</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1161,</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>XIV</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>96963</v>
+      </c>
+      <c r="C7" t="n">
+        <v>101965</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>YNL284C-B:XIV:-|13|5308:288:5289|truncation|ATG</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>96963</v>
+      </c>
+      <c r="H7" t="n">
+        <v>101965</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>3963,1038,</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>